--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>分母を認定者数にすると3年計で10.2％低く出る</t>
+          <t>見える化の3段連鎖（第1号×認定率×利用率）に組み替えると3年計で1.0％低く出る（月額59円）。基準期間が断層をまたぐ場合は10.5％低く出る</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>±1.5％で月額±93円</t>
+          <t>±1.5％で月額±92円</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>5.963％</t>
+          <t>6.148％</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>第9期計画の公表値からの逆算。第10期の全国値は国の基本指針で示される</t>
+          <t>第9期計画の公表値からの逆算。第10期の全国値は国の基本指針で示される。基数は標準給付費見込額のみ（見える化システムの算式）</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>1ポイント下がると月額+290円</t>
+          <t>1ポイント下がると月額+281円</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>1％で月額+3.7円</t>
+          <t>1％で月額+4.2円</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>※ 幅は、標準給付費3年計3,286,398千円・地域支援事業費191,749千円・補正後被保険者数9,798人・予定収納率99.35％のもとでの保険料基準額（月額6,569円）からの変化。</t>
+          <t>※ 幅は、標準給付費3年計3,286,398千円・地域支援事業費191,749千円・補正後被保険者数9,798人・予定収納率99.35％のもとでの保険料基準額（月額6,570円）からの変化。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_基準期間の判定" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_地域支援事業費" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_据え置いた前提" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_必要利用定員総数" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1937,6 +1938,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>町内定員（令和7年度）</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度の利用（人/月）</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度の見込</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度の見込</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度の見込</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>必要利用定員総数（案）</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>現行定員を維持する。見込量に対し余力があり、定員は制約として働いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>町内に事業所がなく、整備の予定もない。0人とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>現行定員を維持する。見込量に対し余力があり、定員は制約として働いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>※ 介護保険法第117条第2項第1号は、認知症対応型共同生活介護・地域密着型特定施設入居者生活介護・地域密着型介護老人福祉施設入所者生活介護の3サービスについて、市町村が定める区域ごとの各年度の必要利用定員総数を定めることを求めている。**努力義務ではなく必須記載事項である。**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>※ 本町は町全域を1つの日常生活圏域とするため、圏域別の区分は生じない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>※ 利用者数は本町の被保険者が1月あたりに利用した人数で、町外の事業所の利用を含む。認知症対応型共同生活介護は介護給付と予防給付の合計。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>※ 町内定員は見える化システムのＤ25〜Ｄ27（令和7年度）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>**※ 認知症対応型共同生活介護は、認知症基本法第18条（保健医療サービス及び福祉サービスの提供体制の整備等）とも直結する。**町内定員98人に対し本町の被保険者の利用は月45人台であり、施設・居住系サービスの自給率59.74％を踏まえると、町内の定員の相当部分が町外の方に利用されていることになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>**※ 第9期計画は「新規施設整備は原則行わず」としていたにもかかわらず、認知症対応型共同生活介護の定員は令和4年度71人から令和6年度98人へ27人増えている。増床の経緯と町外利用の割合を町に確認したうえで確定する。**</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_地域支援事業費" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_据え置いた前提" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_必要利用定員総数" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_地域支援事業の量" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -120,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -243,6 +244,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2136,6 +2143,620 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>出所・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>総合事業</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>訪問介護相当サービス</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>1月あたり利用者数（人）</t>
+        </is>
+      </c>
+      <c r="D2" s="43" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E2" s="43" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F2" s="43" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G2" s="43" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H2" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>国保連月報の総合事業コード。令和6・7年度の第1号被保険者1人当たりの件数率の平均を第10期将来推計用推計人口に乗じた</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>総合事業</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>通所介護相当サービス</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>1月あたり利用者数（人）</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E3" s="43" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="F3" s="43" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G3" s="43" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H3" s="43" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>国保連月報の総合事業コード。令和6・7年度の第1号被保険者1人当たりの件数率の平均を第10期将来推計用推計人口に乗じた</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>総合事業</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメント</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>年間件数</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="n">
+        <v>570</v>
+      </c>
+      <c r="E4" s="43" t="n">
+        <v>545</v>
+      </c>
+      <c r="F4" s="43" t="n">
+        <v>552.6</v>
+      </c>
+      <c r="G4" s="43" t="n">
+        <v>551</v>
+      </c>
+      <c r="H4" s="43" t="n">
+        <v>549.4</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>国保連月報の総合事業コード。令和6・7年度の第1号被保険者1人当たりの件数率の平均を第10期将来推計用推計人口に乗じた</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>総合事業</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>訪問型サービスA（緩和した基準）</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>1月あたり利用者数（人）</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="44" t="n"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>国保連月報では令和6年度以降0件。実施の有無を町に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>総合事業</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>通所型サービスA（緩和した基準）</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>1月あたり利用者数（人）</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="44" t="n"/>
+      <c r="H6" s="44" t="n"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>総合事業</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>その他の生活支援サービス</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>年間延べ利用者数（人）</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>国保連月報では0件。配食・見守り等を総合事業で実施しているかを町に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>一般介護予防事業</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>介護予防普及啓発事業</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>年間開催回数・延べ参加者数</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>**町の事業実績が要る（依頼票H3）。**令和6年度の一般介護予防事業費が5,305千円と前年の5.3倍に増えており、何の事業かとあわせて確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>一般介護予防事業</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>地域介護予防活動支援事業（通いの場）</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>箇所数・年間延べ参加者数</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>**見える化では週1回以上が平成28年度以降0か所である一方、令和7年度調査では週1回以上の参加が5.5％（高齢者人口換算で約190人）。実態の確認が要る**</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>一般介護予防事業</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>地域リハビリテーション活動支援事業</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>年間派遣回数</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>町の事業実績が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>総合相談支援業務</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>年間相談件数</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="44" t="n"/>
+      <c r="H11" s="44" t="n"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>町の事業実績が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>権利擁護業務</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>年間対応件数</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="44" t="n"/>
+      <c r="H12" s="44" t="n"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>町の事業実績が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>包括的・継続的ケアマネジメント支援業務</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>地域ケア会議の年間開催回数</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>町の事業実績が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携推進事業</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>年間相談件数・研修回数</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="44" t="n"/>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>町の事業実績が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>生活支援体制整備事業</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>生活支援コーディネーター配置数・協議体の開催回数</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
+      <c r="H15" s="44" t="n"/>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>町の事業実績が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>初期集中支援チームの対象者把握件数・地域支援推進員の配置数・認知症カフェの箇所数</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="44" t="n"/>
+      <c r="H16" s="44" t="n"/>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>**見える化の直近値は令和5年度（訪問実績0件）・令和6年3月（推進員4人）・令和6年4月（カフェ1か所）。令和6・7年度の実績が要る（依頼票H9）**</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>任意事業</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>家族介護支援事業ほか</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>年間実施回数・利用者数</t>
+        </is>
+      </c>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>【町データ待ち】</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="44" t="n"/>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>町の事業実績が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>**※ 介護保険法第117条第2項第2号は「各年度の地域支援事業の量の見込み」を計画に定めることを求めている。**同項が別に求める費用の見込み（08_地域支援事業費）とは別の記載事項であり、努力義務ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>※ 国保連月報から量を出せるのは介護予防・生活支援サービス事業の3事業だけで、一般介護予防事業・包括的支援事業・任意事業は町の事業実績を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>※ 出せる3事業は、給付の見込量と同じ方法で延ばした。令和6・7年度の第1号被保険者1人当たりの件数率の平均を第10期将来推計用推計人口に乗じている。総合事業は月報が令和6年度からしか取れないため、基準期間は2年である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>**※ 通いの場は、見える化では週1回以上が平成28年度以降0か所である一方、令和7年度調査では週1回以上の参加が5.5％（高齢者人口換算で約190人）ある。**量の見込みを置く前に実態の確認が要る（依頼票H3）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260915.xlsx
@@ -19,7 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_据え置いた前提" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_必要利用定員総数" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_地域支援事業の量" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_令和8年度の置き方" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,11 +29,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0％"/>
     <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -121,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -251,6 +253,16 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2757,6 +2769,299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の置き方</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>対令和7年度</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度（千円）</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>据え置き</t>
+        </is>
+      </c>
+      <c r="B2" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="25" t="n">
+        <v>1005144</v>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>令和7年度の実績をそのまま置く（変化0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>令和6→令和7を延長</t>
+        </is>
+      </c>
+      <c r="B3" s="45" t="n">
+        <v>0.9255</v>
+      </c>
+      <c r="C3" s="25" t="n">
+        <v>930309</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>令和6年度1,085,998千円→令和7年度1,005,144千円の比をもう1年延ばす。**断層を含んだ落ちであり過小になる**</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>現行方式</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n">
+        <v>1.0171</v>
+      </c>
+      <c r="C4" s="25" t="n">
+        <v>1022364</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>令和5〜7年度の利用率の平均×令和8年度の推計人口。**3年平均が下がり続けている系列を上に引いている**</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>月報の実績</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
+        <v>0.9598</v>
+      </c>
+      <c r="C5" s="47" t="n">
+        <v>964745</v>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>国保連月報の令和8年度4〜6月提供分256,885,163円と前年の同じ月267,642,209円の比。**3か月分の実績による**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>■ 令和8年度を基点とした第10期（自然体推計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>現行（令和5〜7年度の利用率平均）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>自然体推計（令和8年度基点）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>令和8年度の総給付費（千円）</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="n"/>
+      <c r="C9" s="48" t="n">
+        <v>964745</v>
+      </c>
+      <c r="D9" s="48" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>令和9年度の総給付費（千円）</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="n">
+        <v>1019104</v>
+      </c>
+      <c r="C10" s="48" t="n">
+        <v>961669</v>
+      </c>
+      <c r="D10" s="48" t="n">
+        <v>-57435</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>令和10年度の総給付費（千円）</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="n">
+        <v>1016139</v>
+      </c>
+      <c r="C11" s="48" t="n">
+        <v>958871</v>
+      </c>
+      <c r="D11" s="48" t="n">
+        <v>-57268</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>令和11年度の総給付費（千円）</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="n">
+        <v>1013175</v>
+      </c>
+      <c r="C12" s="48" t="n">
+        <v>956074</v>
+      </c>
+      <c r="D12" s="48" t="n">
+        <v>-57101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>総給付費 3年計（千円）</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="n">
+        <v>3048418</v>
+      </c>
+      <c r="C13" s="48" t="n">
+        <v>2876614</v>
+      </c>
+      <c r="D13" s="48" t="n">
+        <v>-171804</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>標準給付費 3年計（千円）</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="n">
+        <v>3286398</v>
+      </c>
+      <c r="C14" s="48" t="n">
+        <v>3101182</v>
+      </c>
+      <c r="D14" s="48" t="n">
+        <v>-185216</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>保険料基準額（月額・円）</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="n">
+        <v>6570</v>
+      </c>
+      <c r="C15" s="48" t="n">
+        <v>6224</v>
+      </c>
+      <c r="D15" s="48" t="n">
+        <v>-346</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　100円未満切上げ</t>
+        </is>
+      </c>
+      <c r="B16" s="48" t="n">
+        <v>6600</v>
+      </c>
+      <c r="C16" s="48" t="n">
+        <v>6300</v>
+      </c>
+      <c r="D16" s="48" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>**※ 見える化システムのワークシートは、1人1月あたり給付費の実績値を令和8年度に置いている。令和8年度の列は1か月分であり、その1か月の水準が第10期の3年間に効く。**</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>**※ 国保連月報で確かめられる。**令和8年度の提供分は審査202605〜202607の3か月あり、前年の同じ提供月と比べると96.0％である。当方の現行方式は実績より6.0％高い。令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>※ 自然体推計は、令和8年度を基点とし第1号被保険者1人当たりの給付費を据え置いて人口で延ばしたもの。**見える化システムの自然体推計（利用率・1人1月あたり給付費の変化を0とする）と同じ構造である。**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>**※ どちらを採るかは協議会にお諮りする。**現行は完結年度（令和7年度）を基準年度とする原則に沿う。自然体推計は令和8年度3か月の実績に裏づけられ、見える化の構造とも合うが、令和8年度は完結年度ではない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
